--- a/tiflow/develop/2.0.0-ballot.1/CodeSystem-ti-environment-codes.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/CodeSystem-ti-environment-codes.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/tiflow-core/CodeSystem/ti-environment-codes</t>
+    <t>https://gematik.de/fhir/tiflow/CodeSystem/ti-environment-codes</t>
   </si>
   <si>
     <t>Version</t>
